--- a/private/planilla-vacaciones-2026.xlsx
+++ b/private/planilla-vacaciones-2026.xlsx
@@ -431,31 +431,31 @@
     <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/25000-29999/25552/texact.htm</t>
   </si>
   <si>
-    <t>Ley 27.802 — nuevo art. 154 LCT (B.O. 6/3/2026)</t>
+    <t>Ley 27.802: nuevo art. 154 LCT (B.O. 6/3/2026)</t>
   </si>
   <si>
     <t>https://servicios.infoleg.gob.ar/infolegInternet/verNorma.do?id=423680</t>
   </si>
   <si>
-    <t>Ley 27.399 — Régimen de feriados nacionales y días no laborables</t>
+    <t>Ley 27.399: Régimen de feriados nacionales y días no laborables</t>
   </si>
   <si>
     <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/280000-284999/281835/norma.htm</t>
   </si>
   <si>
-    <t>Decreto 614/2025 — traslado de los feriados que caen fin de semana</t>
+    <t>Decreto 614/2025: traslado de los feriados que caen fin de semana</t>
   </si>
   <si>
     <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/330457/20250828</t>
   </si>
   <si>
-    <t>Resolución 164/2025 — días no laborables con fines turísticos 2026</t>
+    <t>Resolución 164/2025: días no laborables con fines turísticos 2026</t>
   </si>
   <si>
     <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/336753/20251226</t>
   </si>
   <si>
-    <t>Calendario oficial de feriados — Jefatura de Gabinete</t>
+    <t>Calendario oficial de feriados: Jefatura de Gabinete</t>
   </si>
   <si>
     <t>https://www.argentina.gob.ar/jefatura/feriados-nacionales-2026</t>
